--- a/data/06_testRagas/testRagas.xlsx
+++ b/data/06_testRagas/testRagas.xlsx
@@ -471,17 +471,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>quel évènement se sont produit le 25 août 2025 à Nice ?</t>
+          <t>quels évènements se sont produit le 25 août 2025 à Nice ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['[]']</t>
+          <t>['[{\'id\': \'1424693-6\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 06-August-2025 à 14:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;none&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Loisirs Séjours Côte d’Azur, 5 ter avenue de la républiquel\'évènement se déroule le 06-August-2025 14:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.283237, \'lat\': 43.706074}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'7053808128e049bbb586721013a39e5c\'}, {\'id\': 78337946, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 25-August-2025 à 10:30:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;Bonjour, Au cour de cet atelier, nous vous aiderons à télécharger nos applications, à naviguer sur celle-ci, apprendre à candidater, vous permettre de vous rendre visible des recruteurs, vous positionner sur une formation, actualiser votre situation, contacter vos conseillers. Le but est de vous rendre acteur de votre retour à l\'emploi en vous permettant d\'être autonome et à l\'aise sur nos outils.A bientôt.&lt;/p&gt;\\n&lt;p&gt;Il existe deux sessions sur lesquels vous pouvez vous autopositionner:- celle de 9 heure&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE CENTRE, 06000 Nicel\'évènement se déroule le 25-August-2025 10:30:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': \'[{ motsCles : ["Aides à l\\\'emploi"]},{ accessibilite : none},{ coordonnees : {\\\'lon\\\': 7.259337, \\\'lat\\\': 43.700478}},{ telephone : none},{ site_web : none}]\', \'model\': \'mistral-embed\', \'rowHash\': \'0d1cf52987d67475d08c424c99b84c27\'}]']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aucun événement ne s'est produit le 25 août 2025 à Nice selon le contexte fourni.</t>
+          <t>L'événement qui s'est produit le **25 août 2025 à Nice** est un atelier d'aide à la maîtrise des outils numériques de France Travail, organisé à l'**Agence NICE CENTRE** de 10h30 à 11h30.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['[{\'id\': 76804754, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'1 jeune  1 solution\' \'Recrutement\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'51501cc970790e7fba85ecdae63bc596\'}, {\'id\': 6940499, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'Job dating\' \'1 jeune  1 solution\' \'Recrutement\' \'Tout public\' \'CDI\'\\n \'en physique\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'0b7e60eea3635675753ea6e8821be9cc\'}]']</t>
+          <t>['[{\'id\': 6940499, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 03-September-2025 à 09:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nicel\'évènement se déroule le 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'Job dating\' \'1 jeune  1 solution\' \'Recrutement\' \'Tout public\' \'CDI\'\\n \'en physique\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'92069873e7ba44403863890c0d63699c\'}, {\'id\': 76804754, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 03-September-2025 à 09:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nicel\'évènement se déroule le 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'1 jeune  1 solution\' \'Recrutement\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'6ded329168a22212badcade010b297dd\'}]']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['[{\'id\': 76804754, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'1 jeune  1 solution\' \'Recrutement\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'51501cc970790e7fba85ecdae63bc596\'}, {\'id\': 6940499, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'Job dating\' \'1 jeune  1 solution\' \'Recrutement\' \'Tout public\' \'CDI\'\\n \'en physique\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'0b7e60eea3635675753ea6e8821be9cc\'}]']</t>
+          <t>['[{\'id\': 6940499, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 03-September-2025 à 09:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nicel\'évènement se déroule le 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'Job dating\' \'1 jeune  1 solution\' \'Recrutement\' \'Tout public\' \'CDI\'\\n \'en physique\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'92069873e7ba44403863890c0d63699c\'}, {\'id\': 76804754, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 03-September-2025 à 09:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nicel\'évènement se déroule le 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'1 jeune  1 solution\' \'Recrutement\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'6ded329168a22212badcade010b297dd\'}]']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'Agence NICE NORD, 06100 Nice. Il est conseillé de prévoir la matinée.</t>
+          <t>L'évènement de PROVALP 3D se déroule le **03 septembre 2025 à 09h00** à l'Agence Nice Nord (06100 Nice). Il est conseillé de se présenter avec un CV et de prévoir la matinée.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['[{\'id\': \'12234330-1\', \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;Le site de consultation des archives est installé dans une ancienne villa privée du XIXe siècle protégée au titre des Monuments historiques. Découvrez lors de votre visite ce palais de marbre autrefois résidence du marchand d\'art Ernest Gambart ainsi que les intérieurs modifiés au début du XXe siècle dans le style néo-Louis XV.&lt;br&gt;Des visites guidées sont organisées et permettent d\'accéder à des espaces exceptionnellement ouverts aux publics.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Accès dans la limite des places disponibles&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Archives municipales de Nice, 9 avenue de Fabron, 06200 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 20-September-2025 10:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.234668, \'lat\': 43.687745}},{ telephone : 04 93 86 77 44},{ site_web : https://archives.nicecotedazur.org}]", \'model\': \'mistral-embed\', \'rowHash\': \'ec1fbb5ebd4bf1c2efb7bb40f76ae196\'}, {\'id\': 21312701, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;La conférence « Terre &amp;amp; Ciel » est destinée à une trentaine de vos élèves et est entièrement prise en charge par notre association Aérométiers. Elle vise à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale, durant 2 heures. Cette conférence interactive permet aux jeunes de réfléchir à leur orientation professionnelle.&lt;br&gt;Pour garantir le bon déroulement de la conférence, certaines conditions doivent être respectées :&lt;/p&gt;\\n&lt;ul&gt;\\n&lt;li&gt;1. 15 élèves minimum - 30 élèves maximum&lt;/li&gt;\\n&lt;li&gt;2. Un format de 2 heures&lt;/li&gt;\\n&lt;li&gt;3. Une salle dédiée&lt;/li&gt;\\n&lt;li&gt;4. La présence d\'un membre de l\'équipe éducative&lt;/li&gt;\\n&lt;li&gt;5. Un tableau, un PC équipé d\'un rétroprojecteur et d\'enceintes pour visionner un PowerPoint et des vidéos.&lt;/li&gt;\\n&lt;/ul&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Parc Impérial, 2 avenue paul arène&lt;br&gt;- L\'évènement aura lieu à la date suivante : 26-November-2025 08:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.251804, \'lat\': 43.708985}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'f27d139e712c9c321daa4b4c350e3ba5\'}]']</t>
+          <t>['[{\'id\': \'12317819-1\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 10:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 10:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'71d73cdbaf327daeb45d6cf3d49a2ba2\'}, {\'id\': \'12317819-2\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 11:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 11:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'a30f5fc42f7ce48bac8b383e4751c81d\'}, {\'id\': \'12317819-3\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 12:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 12:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'01dc480214161cad5f14ad37ce2e93d0\'}, {\'id\': \'12317819-4\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 13:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 13:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'af81447cc4bc5401b2b04b5384aa5be9\'}, {\'id\': \'12317819-5\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 14:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 14:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'a89ea89769eb221320e60e08fdfaf810\'}, {\'id\': 21312701, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 26-November-2025 à 08:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;La conférence « Terre &amp;amp; Ciel » est destinée à une trentaine de vos élèves et est entièrement prise en charge par notre association Aérométiers. Elle vise à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale, durant 2 heures. Cette conférence interactive permet aux jeunes de réfléchir à leur orientation professionnelle.&lt;br&gt;Pour garantir le bon déroulement de la conférence, certaines conditions doivent être respectées :&lt;/p&gt;\\n&lt;ul&gt;\\n&lt;li&gt;1. 15 élèves minimum - 30 élèves maximum&lt;/li&gt;\\n&lt;li&gt;2. Un format de 2 heures&lt;/li&gt;\\n&lt;li&gt;3. Une salle dédiée&lt;/li&gt;\\n&lt;li&gt;4. La présence d\'un membre de l\'équipe éducative&lt;/li&gt;\\n&lt;li&gt;5. Un tableau, un PC équipé d\'un rétroprojecteur et d\'enceintes pour visionner un PowerPoint et des vidéos.&lt;/li&gt;\\n&lt;/ul&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Parc Impérial, 2 avenue paul arènel\'évènement se déroule le 26-November-2025 08:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.251804, \'lat\': 43.708985}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'11d5f65eca78c4ee084745cbd24bff09\'}]']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>La conférence « Terre &amp; Ciel » destinée à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale s'est déroulée au Lycée Parc Impérial le **26 novembre 2025**.</t>
+          <t>Une conférence intitulée **"Terre &amp; Ciel"** sur les métiers du secteur aérien et de l’industrie aéronautique et spatiale s'est déroulée le **26 novembre 2025** au Lycée Parc Impérial à Nice.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0.9999999999</v>

--- a/data/06_testRagas/testRagas.xlsx
+++ b/data/06_testRagas/testRagas.xlsx
@@ -476,12 +476,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['[{\'id\': \'1424693-6\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 06-August-2025 à 14:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;none&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Loisirs Séjours Côte d’Azur, 5 ter avenue de la républiquel\'évènement se déroule le 06-August-2025 14:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.283237, \'lat\': 43.706074}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'7053808128e049bbb586721013a39e5c\'}, {\'id\': 78337946, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 25-August-2025 à 10:30:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;Bonjour, Au cour de cet atelier, nous vous aiderons à télécharger nos applications, à naviguer sur celle-ci, apprendre à candidater, vous permettre de vous rendre visible des recruteurs, vous positionner sur une formation, actualiser votre situation, contacter vos conseillers. Le but est de vous rendre acteur de votre retour à l\'emploi en vous permettant d\'être autonome et à l\'aise sur nos outils.A bientôt.&lt;/p&gt;\\n&lt;p&gt;Il existe deux sessions sur lesquels vous pouvez vous autopositionner:- celle de 9 heure&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE CENTRE, 06000 Nicel\'évènement se déroule le 25-August-2025 10:30:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': \'[{ motsCles : ["Aides à l\\\'emploi"]},{ accessibilite : none},{ coordonnees : {\\\'lon\\\': 7.259337, \\\'lat\\\': 43.700478}},{ telephone : none},{ site_web : none}]\', \'model\': \'mistral-embed\', \'rowHash\': \'0d1cf52987d67475d08c424c99b84c27\'}]']</t>
+          <t>['[]']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>L'événement qui s'est produit le **25 août 2025 à Nice** est un atelier d'aide à la maîtrise des outils numériques de France Travail, organisé à l'**Agence NICE CENTRE** de 10h30 à 11h30.</t>
+          <t>L'événement qui s'est produit le **25 août 2025 à Nice** est un atelier d'aide à l'utilisation des applications de France Travail, destiné à rendre les utilisateurs autonomes dans leurs démarches d'emploi.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L'évènement de PROVALP 3D se déroule le **03 septembre 2025 à 09h00** à l'Agence Nice Nord (06100 Nice). Il est conseillé de se présenter avec un CV et de prévoir la matinée.</t>
+          <t>L'évènement de PROVALP 3D se déroule le **03 septembre 2025 à 09h00** à l'Agence NICE NORD, 06100 Nice.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['[{\'id\': \'12317819-1\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 10:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 10:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'71d73cdbaf327daeb45d6cf3d49a2ba2\'}, {\'id\': \'12317819-2\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 11:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 11:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'a30f5fc42f7ce48bac8b383e4751c81d\'}, {\'id\': \'12317819-3\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 12:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 12:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'01dc480214161cad5f14ad37ce2e93d0\'}, {\'id\': \'12317819-4\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 13:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 13:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'af81447cc4bc5401b2b04b5384aa5be9\'}, {\'id\': \'12317819-5\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 14:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 14:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'a89ea89769eb221320e60e08fdfaf810\'}, {\'id\': 21312701, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 26-November-2025 à 08:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;La conférence « Terre &amp;amp; Ciel » est destinée à une trentaine de vos élèves et est entièrement prise en charge par notre association Aérométiers. Elle vise à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale, durant 2 heures. Cette conférence interactive permet aux jeunes de réfléchir à leur orientation professionnelle.&lt;br&gt;Pour garantir le bon déroulement de la conférence, certaines conditions doivent être respectées :&lt;/p&gt;\\n&lt;ul&gt;\\n&lt;li&gt;1. 15 élèves minimum - 30 élèves maximum&lt;/li&gt;\\n&lt;li&gt;2. Un format de 2 heures&lt;/li&gt;\\n&lt;li&gt;3. Une salle dédiée&lt;/li&gt;\\n&lt;li&gt;4. La présence d\'un membre de l\'équipe éducative&lt;/li&gt;\\n&lt;li&gt;5. Un tableau, un PC équipé d\'un rétroprojecteur et d\'enceintes pour visionner un PowerPoint et des vidéos.&lt;/li&gt;\\n&lt;/ul&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Parc Impérial, 2 avenue paul arènel\'évènement se déroule le 26-November-2025 08:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.251804, \'lat\': 43.708985}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'11d5f65eca78c4ee084745cbd24bff09\'}]']</t>
+          <t>['[{\'id\': \'12317819-1\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 10:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 10:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'71d73cdbaf327daeb45d6cf3d49a2ba2\'}, {\'id\': \'12317819-3\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 12:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 12:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'01dc480214161cad5f14ad37ce2e93d0\'}, {\'id\': \'12317819-4\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 13:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 13:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'af81447cc4bc5401b2b04b5384aa5be9\'}, {\'id\': \'12317819-2\', \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 20-September-2025 à 11:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;&lt;strong&gt;À l’occasion des Journées Européennes du Patrimoine, le lycée hôtelier Jeanne et Paul Augier ouvre ses portes au public pour une immersion au cœur de l’excellence de la formation hôtelière et de tourisme.&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;👉 Au programme :&lt;/strong&gt;&lt;br&gt;Une visite guidée des coulisses du lycée (cuisines, restaurants d\'application, chambres pédagogiques, etc.), menée par nos étudiants passionnés,&lt;br&gt;Une démonstration culinaire suivie d’une dégustation de spécialités niçoises, préparées par nos élèves de cuisine.&lt;br&gt;&lt;strong&gt;Venez découvrir l’envers du décor, échanger avec les élèves et enseignants, et goûter au savoir-faire de la future génération de professionnels de l’hôtellerie et de la gastronomie !&lt;/strong&gt;&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : Durée des visites guidées : 1h ; Groupe de 20 personnes maximum&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Jeanne et Paul AUGIER, 163 boulevard rené Cassin, 06200 NICE, 163 BOULEVARD RENE CASSIN 06200 NICEl\'évènement se déroule le 20-September-2025 11:00:00&lt;br&gt;- l\'évènement durera : 0 days 01:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : [\'handicap moteur\']},{ coordonnees : {\'lon\': 7.21217, \'lat\': 43.668241}},{ telephone : 04 93 72 77 77},{ site_web : https://www.lycee-paul-augier.com/}]", \'model\': \'mistral-embed\', \'rowHash\': \'a30f5fc42f7ce48bac8b383e4751c81d\'}, {\'id\': 21312701, \'text\': "&lt;h1&gt;Date de l\'évènement : &lt;/h1&gt; &lt;p&gt;l\'évènement se déroule le 26-November-2025 à 08:00:00&lt;/p&gt;&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;&lt;p&gt;La conférence « Terre &amp;amp; Ciel » est destinée à une trentaine de vos élèves et est entièrement prise en charge par notre association Aérométiers. Elle vise à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale, durant 2 heures. Cette conférence interactive permet aux jeunes de réfléchir à leur orientation professionnelle.&lt;br&gt;Pour garantir le bon déroulement de la conférence, certaines conditions doivent être respectées :&lt;/p&gt;\\n&lt;ul&gt;\\n&lt;li&gt;1. 15 élèves minimum - 30 élèves maximum&lt;/li&gt;\\n&lt;li&gt;2. Un format de 2 heures&lt;/li&gt;\\n&lt;li&gt;3. Une salle dédiée&lt;/li&gt;\\n&lt;li&gt;4. La présence d\'un membre de l\'équipe éducative&lt;/li&gt;\\n&lt;li&gt;5. Un tableau, un PC équipé d\'un rétroprojecteur et d\'enceintes pour visionner un PowerPoint et des vidéos.&lt;/li&gt;\\n&lt;/ul&gt;&lt;h1&gt;Informations supplémentaires : &lt;/p&gt;&lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Parc Impérial, 2 avenue paul arènel\'évènement se déroule le 26-November-2025 08:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.251804, \'lat\': 43.708985}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'11d5f65eca78c4ee084745cbd24bff09\'}]']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Une conférence intitulée **"Terre &amp; Ciel"** sur les métiers du secteur aérien et de l’industrie aéronautique et spatiale s'est déroulée le **26 novembre 2025** au Lycée Parc Impérial à Nice.</t>
+          <t>La conférence « Terre &amp; Ciel » destinée à une trentaine d'élèves pour découvrir les métiers du secteur aérien ainsi que de l'industrie aéronautique et spatiale s'est déroulée au Lycée Parc Impérial le **26 novembre 2025**.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.9999999999</v>
